--- a/launch/2026-10/import/otto-ie-part2.xlsx
+++ b/launch/2026-10/import/otto-ie-part2.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU18"/>
+  <dimension ref="A1:AU22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="35" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="21" customWidth="1" min="13" max="13"/>
@@ -452,10 +452,10 @@
     <col width="26" customWidth="1" min="30" max="30"/>
     <col width="17" customWidth="1" min="31" max="31"/>
     <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="35" customWidth="1" min="33" max="33"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
     <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="30" customWidth="1" min="36" max="36"/>
+    <col width="28" customWidth="1" min="36" max="36"/>
     <col width="26" customWidth="1" min="37" max="37"/>
     <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
@@ -726,7 +726,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>IE · a4 · You run it, Otto posts</t>
+          <t>IE · a4 · The ads Otto makes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>ie-a4-big-v</t>
+          <t>ie-a4-texts-v</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>You run the business. Otto posts.</t>
+          <t>The ads Otto makes for you</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Otto plans your month, writes your posts, makes your reels and runs your ads. You tap approve. About 30 minutes a week.</t>
+          <t>Product ads, offers, comparisons, story ads. Otto designs your ads in your brand and runs them. You approve each one.</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Designed, run and reported</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a4-big-v</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a4-texts-v</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>ie-a4-big-v-9x16.mp4</t>
+          <t>ie-a4-texts-v-9x16.mp4</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -909,7 +909,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>IE · a4 · You run it, Otto posts</t>
+          <t>IE · a4 · The ads Otto makes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>ie-a4-versus-v</t>
+          <t>ie-a4-big-v</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>For owners with no marketing team</t>
+          <t>Your ads, designed and run by Otto</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>For the plumber under a sink all day and the café that closes at five: Otto does the marketing, you make the calls.</t>
+          <t>Boosting a random post isn't an ad campaign. Otto makes proper ads for every angle and tests them side by side.</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Designed, run and reported</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a4-versus-v</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a4-big-v</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>ie-a4-versus-v-9x16.mp4</t>
+          <t>ie-a4-big-v-9x16.mp4</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1092,7 +1092,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>IE · a4 · You run it, Otto posts</t>
+          <t>IE · a4 · The ads Otto makes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>ie-a4-texts-v</t>
+          <t>ie-a4-versus-v</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>You run the business. Otto posts.</t>
+          <t>The ads Otto makes for you</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Sign in, give Otto your website address, answer four questions at most, and your first posts are ready within 24 hours.</t>
+          <t>Ads for your feed and your stories, made from your own website. Plus your posts and reels, for €79 a month.</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Designed, run and reported</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a4-texts-v</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a4-versus-v</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>ie-a4-texts-v-9x16.mp4</t>
+          <t>ie-a4-versus-v-9x16.mp4</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1275,7 +1275,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>IE · a4 · You run it, Otto posts</t>
+          <t>IE · a4 · The ads Otto makes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>For owners with no marketing team</t>
+          <t>Your ads, designed and run by Otto</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Otto plans your month, writes your posts, makes your reels and runs your ads. You tap approve. About 30 minutes a week.</t>
+          <t>Product ads, offers, comparisons, story ads. Otto designs your ads in your brand and runs them. You approve each one.</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Designed, run and reported</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1458,7 +1458,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>IE · a4 · You run it, Otto posts</t>
+          <t>IE · a4 · The ads Otto makes</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>You run the business. Otto posts.</t>
+          <t>The ads Otto makes for you</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>For the plumber under a sink all day and the café that closes at five: Otto does the marketing, you make the calls.</t>
+          <t>Boosting a random post isn't an ad campaign. Otto makes proper ads for every angle and tests them side by side.</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Designed, run and reported</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1641,7 +1641,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>IE · a4 · You run it, Otto posts</t>
+          <t>IE · a4 · The ads Otto makes</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>For owners with no marketing team</t>
+          <t>Your ads, designed and run by Otto</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Sign in, give Otto your website address, answer four questions at most, and your first posts are ready within 24 hours.</t>
+          <t>Ads for your feed and your stories, made from your own website. Plus your posts and reels, for €79 a month.</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Posts, reels and ads by Otto</t>
+          <t>Designed, run and reported</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1824,7 +1824,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>IE · a5 · 7 days free</t>
+          <t>IE · a4 · The ads Otto makes</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>ie-a5-big-v</t>
+          <t>ie-a4-premium</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Try Otto free for 7 days</t>
+          <t>The ads Otto makes for you</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Try Otto free for 7 days. Sign in with Google, give it your website, and your first posts are ready within 24 hours.</t>
+          <t>Product ads, offers, comparisons, story ads. Otto designs your ads in your brand and runs them. You approve each one.</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7 days free, no card</t>
+          <t>Designed, run and reported</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1950,22 +1950,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>ads-1x1.jpg</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Video Page Post Ad</t>
+          <t>Link Page Post Ad</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-big-v</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>ie-a5-big-v-9x16.mp4</t>
-        </is>
-      </c>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a4-premium</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>SIGN_UP</t>
+          <t>LEARN_MORE</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
@@ -2007,7 +2007,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>IE · a5 · 7 days free</t>
+          <t>IE · a5 · You run it, Otto posts</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>ie-a5-texts-v</t>
+          <t>ie-a5-big-v</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>No card needed</t>
+          <t>You run the business. Otto posts.</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>After 7 days you decide. Nothing is charged automatically, and if you pick a plan, everything Otto made carries on.</t>
+          <t>Otto plans your month, writes your posts, makes your reels and stories, and posts them on time. You tap approve.</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7 days free, no card</t>
+          <t>Posts, reels and stories</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-texts-v</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-big-v</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>ie-a5-texts-v-9x16.mp4</t>
+          <t>ie-a5-big-v-9x16.mp4</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SIGN_UP</t>
+          <t>LEARN_MORE</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
@@ -2190,7 +2190,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>IE · a5 · 7 days free</t>
+          <t>IE · a5 · You run it, Otto posts</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>ie-a5-versus-v</t>
+          <t>ie-a5-texts-v</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Try Otto free for 7 days</t>
+          <t>Posts, reels and stories, every week</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Your first week of posts, stories and reels, approvals from your phone and the 7:35 report. Free for 7 days, no card.</t>
+          <t>Every week: carousels, reels, stories, offers and how-tos, made from your own website, in your brand.</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7 days free, no card</t>
+          <t>Posts, reels and stories</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-versus-v</t>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-texts-v</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>ie-a5-versus-v-9x16.mp4</t>
+          <t>ie-a5-texts-v-9x16.mp4</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>SIGN_UP</t>
+          <t>LEARN_MORE</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
@@ -2373,7 +2373,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>IE · a5 · 7 days free</t>
+          <t>IE · a5 · You run it, Otto posts</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ie-a5-offer</t>
+          <t>ie-a5-versus-v</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>No card needed</t>
+          <t>You run the business. Otto posts.</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Try Otto free for 7 days. Sign in with Google, give it your website, and your first posts are ready within 24 hours.</t>
+          <t>For the plumber under a sink all day and the café that closes at five: Otto does the posts, you make the calls.</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7 days free, no card</t>
+          <t>Posts, reels and stories</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2499,22 +2499,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>ie-a5-offer-4x5.jpg</t>
-        </is>
-      </c>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Link Page Post Ad</t>
+          <t>Video Page Post Ad</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-offer</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-versus-v</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>ie-a5-versus-v-9x16.mp4</t>
+        </is>
+      </c>
       <c r="AR11" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SIGN_UP</t>
+          <t>LEARN_MORE</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
@@ -2556,7 +2556,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>IE · a5 · 7 days free</t>
+          <t>IE · a5 · You run it, Otto posts</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Try Otto free for 7 days</t>
+          <t>Posts, reels and stories, every week</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>After 7 days you decide. Nothing is charged automatically, and if you pick a plan, everything Otto made carries on.</t>
+          <t>Otto plans your month, writes your posts, makes your reels and stories, and posts them on time. You tap approve.</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7 days free, no card</t>
+          <t>Posts, reels and stories</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>SIGN_UP</t>
+          <t>LEARN_MORE</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
@@ -2739,7 +2739,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>IE · a5 · 7 days free</t>
+          <t>IE · a5 · You run it, Otto posts</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>No card needed</t>
+          <t>You run the business. Otto posts.</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Your first week of posts, stories and reels, approvals from your phone and the 7:35 report. Free for 7 days, no card.</t>
+          <t>Every week: carousels, reels, stories, offers and how-tos, made from your own website, in your brand.</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>7 days free, no card</t>
+          <t>Posts, reels and stories</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>SIGN_UP</t>
+          <t>LEARN_MORE</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -2922,7 +2922,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>IE · a6 · Christmas, sorted early</t>
+          <t>IE · a5 · You run it, Otto posts</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>ie-a6-texts-v</t>
+          <t>ie-a5-checklist</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Christmas, sorted before the rush</t>
+          <t>Posts, reels and stories, every week</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Christmas is your busiest month and your least free one. Otto plans the run-up ahead, so you can just work it.</t>
+          <t>For the plumber under a sink all day and the café that closes at five: Otto does the posts, you make the calls.</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Your busy season, planned</t>
+          <t>Posts, reels and stories</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3048,22 +3048,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>ie-a5-checklist-4x5.jpg</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Video Page Post Ad</t>
+          <t>Link Page Post Ad</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-texts-v</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>ie-a6-texts-v-9x16.mp4</t>
-        </is>
-      </c>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-checklist</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -3105,7 +3105,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>IE · a6 · Christmas, sorted early</t>
+          <t>IE · a5 · You run it, Otto posts</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>ie-a6-big-v</t>
+          <t>ie-a5-premium</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Your busy season, planned ahead</t>
+          <t>You run the business. Otto posts.</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Gift vouchers, Christmas opening hours, the festive menu: Otto plans them for the hours your customers are online.</t>
+          <t>Otto plans your month, writes your posts, makes your reels and stories, and posts them on time. You tap approve.</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Your busy season, planned</t>
+          <t>Posts, reels and stories</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3231,22 +3231,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>posts-1x1.jpg</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Video Page Post Ad</t>
+          <t>Link Page Post Ad</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-big-v</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>ie-a6-big-v-9x16.mp4</t>
-        </is>
-      </c>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a5-premium</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -3288,7 +3288,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>IE · a6 · Christmas, sorted early</t>
+          <t>IE · a6 · Launching? 7 days free</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Christmas, sorted before the rush</t>
+          <t>Launching? Try Otto free for 7 days</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Start now and Otto lines up your posts, reels and ads for the busy weeks. You approve it all in advance.</t>
+          <t>Launching a business? Marketing is handled from day one: posts, stories, reels and ads. Try Otto free for 7 days.</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Your busy season, planned</t>
+          <t>7 days free, no card</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>LEARN_MORE</t>
+          <t>SIGN_UP</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
@@ -3471,7 +3471,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>IE · a6 · Christmas, sorted early</t>
+          <t>IE · a6 · Launching? 7 days free</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ie-a6-before</t>
+          <t>ie-a6-texts-v</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Your busy season, planned ahead</t>
+          <t>7 days free. Then €79 a month.</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Christmas is your busiest month and your least free one. Otto plans the run-up ahead, so you can just work it.</t>
+          <t>7 days free, no card. Then €79 a month (excl. VAT), monthly, cancel anytime. Nothing is charged automatically.</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Your busy season, planned</t>
+          <t>7 days free, no card</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3597,22 +3597,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>ie-a6-before-4x5.jpg</t>
-        </is>
-      </c>
+      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Link Page Post Ad</t>
+          <t>Video Page Post Ad</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-before</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr"/>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-texts-v</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>ie-a6-texts-v-9x16.mp4</t>
+        </is>
+      </c>
       <c r="AR17" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>LEARN_MORE</t>
+          <t>SIGN_UP</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
@@ -3654,7 +3654,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>IE · a6 · Christmas, sorted early</t>
+          <t>IE · a6 · Launching? 7 days free</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3737,81 +3737,813 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
+          <t>ie-a6-versus-v</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Launching? Try Otto free for 7 days</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>New café, B&amp;B or trade? Otto does the posts and the ads from day one. Your first week is ready within minutes.</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>{DOMAIN}</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>7 days free, no card</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Video Page Post Ad</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-versus-v</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>ie-a6-versus-v-9x16.mp4</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>x:{INSTAGRAM_ID}</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SIGN_UP</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>{IE_CAMPAIGN_ID}</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OTTO · IE · Launch · 2026-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>IE · a6 · Launching? 7 days free</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>WEBSITE</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>o:{PAGE_ID}</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>https://{DOMAIN}/</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>65</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>mobile, desktop</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>[{"event_type":"CLICK_THROUGH","window_days":7},{"event_type":"VIEW_THROUGH","window_days":1}]</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>ie-a6-offer</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>7 days free. Then €79 a month.</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Launching a business? Marketing is handled from day one: posts, stories, reels and ads. Try Otto free for 7 days.</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>{DOMAIN}</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>7 days free, no card</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>ie-a6-offer-4x5.jpg</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Link Page Post Ad</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-offer</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>x:{INSTAGRAM_ID}</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SIGN_UP</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>{IE_CAMPAIGN_ID}</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OTTO · IE · Launch · 2026-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>IE · a6 · Launching? 7 days free</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>WEBSITE</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>o:{PAGE_ID}</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>https://{DOMAIN}/</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>65</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>mobile, desktop</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>[{"event_type":"CLICK_THROUGH","window_days":7},{"event_type":"VIEW_THROUGH","window_days":1}]</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
           <t>ie-a6-product</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Christmas, sorted before the rush</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Gift vouchers, Christmas opening hours, the festive menu: Otto plans them for the hours your customers are online.</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Launching? Try Otto free for 7 days</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>7 days free, no card. Then €79 a month (excl. VAT), monthly, cancel anytime. Nothing is charged automatically.</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>{DOMAIN}</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>Your busy season, planned</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>7 days free, no card</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
         <is>
           <t>tp:{PIXEL_ID}</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
         <is>
           <t>ie-a6-product-4x5.jpg</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>Link Page Post Ad</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
+      <c r="AP20" t="inlineStr">
         <is>
           <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-product</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr">
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr">
         <is>
           <t>x:{INSTAGRAM_ID}</t>
         </is>
       </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>LEARN_MORE</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SIGN_UP</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AU18" t="inlineStr">
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>{IE_CAMPAIGN_ID}</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OTTO · IE · Launch · 2026-10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>IE · a6 · Launching? 7 days free</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>WEBSITE</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>o:{PAGE_ID}</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>https://{DOMAIN}/</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>65</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>mobile, desktop</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>[{"event_type":"CLICK_THROUGH","window_days":7},{"event_type":"VIEW_THROUGH","window_days":1}]</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>ie-a6-checklist</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>7 days free. Then €79 a month.</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>New café, B&amp;B or trade? Otto does the posts and the ads from day one. Your first week is ready within minutes.</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>{DOMAIN}</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>7 days free, no card</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>ie-a6-checklist-4x5.jpg</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Link Page Post Ad</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-checklist</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>x:{INSTAGRAM_ID}</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SIGN_UP</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>{IE_CAMPAIGN_ID}</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OTTO · IE · Launch · 2026-10</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>IE · a6 · Launching? 7 days free</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>10/03/2026 12:00:00 am</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>4</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>WEBSITE</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>o:{PAGE_ID}</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>COMPLETE_REGISTRATION</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>https://{DOMAIN}/</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>25</v>
+      </c>
+      <c r="W22" t="n">
+        <v>65</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>mobile, desktop</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>OFFSITE_CONVERSIONS</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>[{"event_type":"CLICK_THROUGH","window_days":7},{"event_type":"VIEW_THROUGH","window_days":1}]</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>ie-a6-premium</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Launching? Try Otto free for 7 days</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Launching a business? Marketing is handled from day one: posts, stories, reels and ads. Try Otto free for 7 days.</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>{DOMAIN}</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>7 days free, no card</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>tp:{PIXEL_ID}</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>launch-1x1.jpg</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Link Page Post Ad</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>utm_source=meta&amp;utm_medium=paid&amp;utm_campaign=otto_ie_launch&amp;utm_content=ie-a6-premium</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>x:{INSTAGRAM_ID}</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SIGN_UP</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
